--- a/Data/EXCEL/Transfer/salemon/202412/1701-salemon-202412.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202412/1701-salemon-202412.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\xls2xlsx\202412\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202412\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E573991B-9D24-421E-BF53-4981074855F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6ED22AE8-2988-45FF-A577-047FB067FC38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" xr2:uid="{9D17C6E4-1E0E-478F-B348-3533EDC6ACED}"/>
+    <workbookView xWindow="2235" yWindow="1695" windowWidth="21600" windowHeight="13425" xr2:uid="{FCEE6A1B-02D0-4A2F-A1DA-E2BACD261BFF}"/>
   </bookViews>
   <sheets>
     <sheet name="1701-salemon-202412" sheetId="2" r:id="rId1"/>
@@ -1255,21 +1255,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8813D7D6-B0DE-4287-AB0D-761F7BC4D598}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB11A6A8-FCB6-4C00-9CF3-58A2F25E9A45}">
   <dimension ref="A1:Q39"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.90625" customWidth="1"/>
-    <col min="2" max="5" width="14.7265625" customWidth="1"/>
-    <col min="6" max="6" width="13.90625" customWidth="1"/>
-    <col min="7" max="7" width="14.7265625" customWidth="1"/>
-    <col min="8" max="10" width="13.90625" customWidth="1"/>
-    <col min="11" max="11" width="14.7265625" customWidth="1"/>
-    <col min="12" max="15" width="13.90625" customWidth="1"/>
-    <col min="16" max="17" width="14.7265625" customWidth="1"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="9.5" customWidth="1"/>
+    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="8" max="10" width="9.5" customWidth="1"/>
+    <col min="11" max="11" width="10" customWidth="1"/>
+    <col min="12" max="15" width="9.5" customWidth="1"/>
+    <col min="16" max="16" width="10" customWidth="1"/>
+    <col min="17" max="17" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
@@ -1296,7 +1297,7 @@
       <c r="P1" s="20"/>
       <c r="Q1" s="21"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="17"/>
       <c r="B2" s="16" t="s">
         <v>4</v>
@@ -1335,7 +1336,7 @@
       </c>
       <c r="Q2" s="21"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="17"/>
       <c r="B3" s="17"/>
       <c r="C3" s="17"/>
@@ -1378,7 +1379,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="18"/>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
@@ -1417,7 +1418,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>45474</v>
       </c>
@@ -1470,7 +1471,7 @@
         <v>4.93</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
         <v>45444</v>
       </c>
@@ -1523,7 +1524,7 @@
         <v>5.93</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>45413</v>
       </c>
@@ -1576,7 +1577,7 @@
         <v>7.97</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
         <v>45383</v>
       </c>
@@ -1629,7 +1630,7 @@
         <v>8.16</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>45352</v>
       </c>
@@ -1682,7 +1683,7 @@
         <v>7.52</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
         <v>45323</v>
       </c>
@@ -1735,7 +1736,7 @@
         <v>10.1</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>45292</v>
       </c>
@@ -1788,7 +1789,7 @@
         <v>18.3</v>
       </c>
     </row>
-    <row r="12" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
         <v>45261</v>
       </c>
@@ -1841,7 +1842,7 @@
         <v>1.38</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>45231</v>
       </c>
@@ -1894,7 +1895,7 @@
         <v>4.08</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11">
         <v>45200</v>
       </c>
@@ -1947,7 +1948,7 @@
         <v>4.0199999999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>45170</v>
       </c>
@@ -2000,7 +2001,7 @@
         <v>4.01</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
         <v>45139</v>
       </c>
@@ -2053,7 +2054,7 @@
         <v>4.84</v>
       </c>
     </row>
-    <row r="17" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>45108</v>
       </c>
@@ -2106,7 +2107,7 @@
         <v>4.84</v>
       </c>
     </row>
-    <row r="18" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
         <v>45078</v>
       </c>
@@ -2159,7 +2160,7 @@
         <v>4.83</v>
       </c>
     </row>
-    <row r="19" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>45047</v>
       </c>
@@ -2212,7 +2213,7 @@
         <v>5.32</v>
       </c>
     </row>
-    <row r="20" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
         <v>45017</v>
       </c>
@@ -2265,7 +2266,7 @@
         <v>6.59</v>
       </c>
     </row>
-    <row r="21" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>44986</v>
       </c>
@@ -2318,7 +2319,7 @@
         <v>8.1199999999999992</v>
       </c>
     </row>
-    <row r="22" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
         <v>44958</v>
       </c>
@@ -2371,7 +2372,7 @@
         <v>9.9700000000000006</v>
       </c>
     </row>
-    <row r="23" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>44927</v>
       </c>
@@ -2424,7 +2425,7 @@
         <v>1.71</v>
       </c>
     </row>
-    <row r="24" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
         <v>44896</v>
       </c>
@@ -2477,7 +2478,7 @@
         <v>5.97</v>
       </c>
     </row>
-    <row r="25" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <v>44866</v>
       </c>
@@ -2530,7 +2531,7 @@
         <v>3.53</v>
       </c>
     </row>
-    <row r="26" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
         <v>44835</v>
       </c>
@@ -2583,7 +2584,7 @@
         <v>3.19</v>
       </c>
     </row>
-    <row r="27" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <v>44805</v>
       </c>
@@ -2636,7 +2637,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="28" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="11">
         <v>44774</v>
       </c>
@@ -2689,7 +2690,7 @@
         <v>1.42</v>
       </c>
     </row>
-    <row r="29" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <v>44743</v>
       </c>
@@ -2742,7 +2743,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="30" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11">
         <v>44713</v>
       </c>
@@ -2795,7 +2796,7 @@
         <v>-0.38</v>
       </c>
     </row>
-    <row r="31" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
         <v>44682</v>
       </c>
@@ -2848,7 +2849,7 @@
         <v>-1.46</v>
       </c>
     </row>
-    <row r="32" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11">
         <v>44652</v>
       </c>
@@ -2901,7 +2902,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="33" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
         <v>44621</v>
       </c>
@@ -2954,7 +2955,7 @@
         <v>-2.88</v>
       </c>
     </row>
-    <row r="34" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="11">
         <v>44593</v>
       </c>
@@ -3007,7 +3008,7 @@
         <v>-8.27</v>
       </c>
     </row>
-    <row r="35" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
         <v>44562</v>
       </c>
@@ -3060,7 +3061,7 @@
         <v>-14.2</v>
       </c>
     </row>
-    <row r="36" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="11">
         <v>44531</v>
       </c>
@@ -3113,7 +3114,7 @@
         <v>-2.04</v>
       </c>
     </row>
-    <row r="37" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
         <v>44501</v>
       </c>
@@ -3166,7 +3167,7 @@
         <v>-1.94</v>
       </c>
     </row>
-    <row r="38" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="11">
         <v>44470</v>
       </c>
@@ -3219,7 +3220,7 @@
         <v>-1.37</v>
       </c>
     </row>
-    <row r="39" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
         <v>44440</v>
       </c>
